--- a/Yearwise_EV_Growth_Analysis.xlsx
+++ b/Yearwise_EV_Growth_Analysis.xlsx
@@ -1,34 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\OneDrive\LMS\3.1\Gruop Project\EDA\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A1E973-6EC0-4128-8BFC-0E18944867A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+  <si>
+    <t>Manufacture Year</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Cumulative EVs</t>
+  </si>
+  <si>
+    <t>Growth Rate (%)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +68,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,325 +370,317 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.26953125" customWidth="1"/>
+    <col min="3" max="3" width="14.08984375" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Manufacture Year</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Cumulative EVs</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Growth Rate (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2">
         <v>2005</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>22</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>22</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3">
         <v>2006</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>7</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>29</v>
       </c>
-      <c r="D3" t="n">
-        <v>-68.18181818181819</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="D3">
+        <v>-68.181818181818187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4">
         <v>2007</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>2</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>31</v>
       </c>
-      <c r="D4" t="n">
-        <v>-71.42857142857143</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="D4">
+        <v>-71.428571428571431</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5">
         <v>2008</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>12</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>43</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>500</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6">
         <v>2009</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>45</v>
       </c>
-      <c r="D6" t="n">
-        <v>-83.33333333333334</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="D6">
+        <v>-83.333333333333343</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7">
         <v>2010</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>9</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>54</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>350</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8">
         <v>2011</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>45</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>99</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>400</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9">
         <v>2012</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>672</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>771</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>1393.333333333333</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10">
         <v>2013</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>1232</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>2003</v>
       </c>
-      <c r="D10" t="n">
-        <v>83.33333333333333</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="D10">
+        <v>83.333333333333329</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11">
         <v>2014</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>1262</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>3265</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>2.435064935064934</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12">
         <v>2015</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>567</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>3832</v>
       </c>
-      <c r="D12" t="n">
-        <v>-55.07131537242472</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+      <c r="D12">
+        <v>-55.071315372424721</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13">
         <v>2016</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>537</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>4369</v>
       </c>
-      <c r="D13" t="n">
-        <v>-5.291005291005291</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
+      <c r="D13">
+        <v>-5.2910052910052912</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14">
         <v>2017</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>479</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>4848</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>-10.80074487895717</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15">
         <v>2018</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>679</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>5527</v>
       </c>
-      <c r="D15" t="n">
-        <v>41.75365344467641</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
+      <c r="D15">
+        <v>41.753653444676409</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16">
         <v>2019</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>291</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>5818</v>
       </c>
-      <c r="D16" t="n">
-        <v>-57.14285714285714</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
+      <c r="D16">
+        <v>-57.142857142857139</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17">
         <v>2020</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>89</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>5907</v>
       </c>
-      <c r="D17" t="n">
-        <v>-69.41580756013745</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
+      <c r="D17">
+        <v>-69.415807560137452</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18">
         <v>2021</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>33</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>5940</v>
       </c>
-      <c r="D18" t="n">
-        <v>-62.92134831460674</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
+      <c r="D18">
+        <v>-62.921348314606739</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19">
         <v>2022</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>910</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>6850</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>2657.575757575758</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20">
         <v>2023</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>1909</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>8759</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>109.7802197802198</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21">
         <v>2024</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>4637</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>13396</v>
       </c>
-      <c r="D21" t="n">
-        <v>142.9020429544264</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
+      <c r="D21">
+        <v>142.90204295442641</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22">
         <v>2025</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>10565</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>23961</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>127.8412766875135</v>
       </c>
     </row>

--- a/Yearwise_EV_Growth_Analysis.xlsx
+++ b/Yearwise_EV_Growth_Analysis.xlsx
@@ -1,55 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\OneDrive\LMS\3.1\Gruop Project\EDA\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A1E973-6EC0-4128-8BFC-0E18944867A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>Manufacture Year</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Cumulative EVs</t>
-  </si>
-  <si>
-    <t>Growth Rate (%)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -68,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -370,317 +408,325 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="15.26953125" customWidth="1"/>
-    <col min="3" max="3" width="14.08984375" customWidth="1"/>
-    <col min="4" max="4" width="14.7265625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Manufacture Year</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Cumulative EVs</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Growth Rate (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-68.18181818181819</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B4" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>2005</v>
-      </c>
-      <c r="B2">
-        <v>22</v>
-      </c>
-      <c r="C2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>2006</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>29</v>
-      </c>
-      <c r="D3">
-        <v>-68.181818181818187</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>2007</v>
-      </c>
-      <c r="B4">
+      <c r="C4" t="n">
+        <v>31</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-71.42857142857143</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" t="n">
+        <v>43</v>
+      </c>
+      <c r="D5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B6" t="n">
         <v>2</v>
       </c>
-      <c r="C4">
-        <v>31</v>
-      </c>
-      <c r="D4">
-        <v>-71.428571428571431</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>2008</v>
-      </c>
-      <c r="B5">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>43</v>
-      </c>
-      <c r="D5">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>2009</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>45</v>
       </c>
-      <c r="D6">
-        <v>-83.333333333333343</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7">
+      <c r="D6" t="n">
+        <v>-83.33333333333334</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>2010</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>9</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>54</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>350</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8">
+    <row r="8">
+      <c r="A8" t="n">
         <v>2011</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>45</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>99</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9">
+    <row r="9">
+      <c r="A9" t="n">
         <v>2012</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>672</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>771</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>1393.333333333333</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10">
+    <row r="10">
+      <c r="A10" t="n">
         <v>2013</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>1232</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>2003</v>
       </c>
-      <c r="D10">
-        <v>83.333333333333329</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11">
+      <c r="D10" t="n">
+        <v>83.33333333333333</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>2014</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>1262</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>3265</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>2.435064935064934</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12">
+    <row r="12">
+      <c r="A12" t="n">
         <v>2015</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>567</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>3832</v>
       </c>
-      <c r="D12">
-        <v>-55.071315372424721</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13">
+      <c r="D12" t="n">
+        <v>-55.07131537242472</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
         <v>2016</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>537</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>4369</v>
       </c>
-      <c r="D13">
-        <v>-5.2910052910052912</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14">
+      <c r="D13" t="n">
+        <v>-5.291005291005291</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>2017</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>479</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>4848</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>-10.80074487895717</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15">
+    <row r="15">
+      <c r="A15" t="n">
         <v>2018</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>679</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>5527</v>
       </c>
-      <c r="D15">
-        <v>41.753653444676409</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16">
+      <c r="D15" t="n">
+        <v>41.75365344467641</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>2019</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>291</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>5818</v>
       </c>
-      <c r="D16">
-        <v>-57.142857142857139</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17">
+      <c r="D16" t="n">
+        <v>-57.14285714285714</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
         <v>2020</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="n">
         <v>89</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>5907</v>
       </c>
-      <c r="D17">
-        <v>-69.415807560137452</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18">
+      <c r="D17" t="n">
+        <v>-69.41580756013745</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
         <v>2021</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="n">
         <v>33</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>5940</v>
       </c>
-      <c r="D18">
-        <v>-62.921348314606739</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19">
+      <c r="D18" t="n">
+        <v>-62.92134831460674</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
         <v>2022</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="n">
         <v>910</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="n">
         <v>6850</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="n">
         <v>2657.575757575758</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20">
+    <row r="20">
+      <c r="A20" t="n">
         <v>2023</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="n">
         <v>1909</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>8759</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>109.7802197802198</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21">
+    <row r="21">
+      <c r="A21" t="n">
         <v>2024</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="n">
         <v>4637</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>13396</v>
       </c>
-      <c r="D21">
-        <v>142.90204295442641</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22">
+      <c r="D21" t="n">
+        <v>142.9020429544264</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
         <v>2025</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="n">
         <v>10565</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="n">
         <v>23961</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="n">
         <v>127.8412766875135</v>
       </c>
     </row>
